--- a/Контакты_для_Влада.xlsx
+++ b/Контакты_для_Влада.xlsx
@@ -672,7 +672,11 @@
           <t>+7 (343) 206-12-06</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr"/>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>info@yarmysheva.ru</t>
+        </is>
+      </c>
       <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -696,7 +700,7 @@
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>Бренд ЯRMYSHEVA, Екатеринбург, пр-кт Ленина, 50Д, оф. 205-208</t>
+          <t>Бренд ЯRMYSHEVA, дизайнерская одежда. Екатеринбург, пр-кт Ленина, 50Д, оф. 205-208</t>
         </is>
       </c>
     </row>
@@ -738,7 +742,11 @@
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr"/>
-      <c r="L5" s="4" t="inlineStr"/>
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>Бывший ген. директор Willsun (торговля лесоматериалами, стройматериалами). Компания ликвидирована</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -789,7 +797,7 @@
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>Депутат Екатеринбургской гор. Думы, адвокат, руководитель фракции «Единой России»</t>
+          <t>Депутат Екатеринбургской гор. Думы VIII созыва, адвокат с 2011 г., руководитель фракции «Единой России». Волонтерский центр ~1000 волонтёров</t>
         </is>
       </c>
     </row>
@@ -808,7 +816,11 @@
           <t>Рутковский Евгений</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr"/>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>+7 (343) 226-02-72</t>
+        </is>
+      </c>
       <c r="F7" s="4" t="inlineStr"/>
       <c r="G7" s="4" t="inlineStr"/>
       <c r="H7" s="4" t="inlineStr">
@@ -830,8 +842,16 @@
 деятельность вспомогательная прочая, связанная с перевозками.</t>
         </is>
       </c>
-      <c r="K7" s="4" t="inlineStr"/>
-      <c r="L7" s="4" t="inlineStr"/>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>kvarta.uralfirm.ru</t>
+        </is>
+      </c>
+      <c r="L7" s="5" t="inlineStr">
+        <is>
+          <t>ООО «КВАРТА» (с 2013 г.), Екатеринбург, пер. Красный, 5, корп. 1, оф. 7. Грузовые перевозки, торговля спецтехникой</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -870,10 +890,14 @@
           <t>Основатель и владелец «Жизньмарт» — российская сеть магазинов кулинарии «у дома», работающая по системе франчайзинга. Сушкоф и пицца - ресторанно-доставочный бизнес</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr"/>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>shrmps-brgrs.ru</t>
+        </is>
+      </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>Основатель «Жизньмарт» (200+ магазинов), «Сушкоф и пицца». Instagram: @ivanzaychenko</t>
+          <t>Основатель «Жизньмарт» (200+ магазинов в РФ), «Сушкоф и пицца», IT-система «Гуляш». Выручка 333 млн (2023). Instagram: @ivanzaychenko</t>
         </is>
       </c>
     </row>
@@ -921,7 +945,7 @@
       </c>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>Директор по трейд-маркетингу Okkam, 17 лет в аналитике для ритейла и FMCG. Москва, Пресненская наб. 6/2</t>
+          <t>Директор по трейд-маркетингу Okkam (ком. группа полного цикла), 17 лет в аналитике для ритейла и FMCG. МГУ. Москва, Пресненская наб. 6/2</t>
         </is>
       </c>
     </row>
@@ -940,8 +964,16 @@
           <t>Невзорова Ирина</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr"/>
-      <c r="F10" s="2" t="inlineStr"/>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>+7 (343) 310-79-35</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>info.novosibirsk@saint-gobain.com</t>
+        </is>
+      </c>
       <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr">
         <is>
@@ -958,8 +990,16 @@
           <t>В 2017 году она перешла в Isover из компании «Бергауф Строительные технологии», где работала с 2004 года.  Isover — бренд теплоизоляционных материалов, принадлежащий международной компании Saint-Gobain.</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr"/>
-      <c r="L10" s="2" t="inlineStr"/>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>isover.ru</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>Работает в Isover (бренд Saint-Gobain, теплоизоляция). Ранее — «Бергауф Строительные технологии». Офис: ул. Черкасская, 25, Екатеринбург</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
@@ -1004,12 +1044,12 @@
       </c>
       <c r="K11" s="5" t="inlineStr">
         <is>
-          <t>https://энергософт.рф; энергософт.рф</t>
+          <t>https://энергософт.рф; энергософт.рф (npcat.ru)</t>
         </is>
       </c>
       <c r="L11" s="5" t="inlineStr">
         <is>
-          <t>ООО ИК «Энергософт», Екатеринбург, пр. Решетникова, 22а, оф. 206. Выручка 867 млн руб.</t>
+          <t>ООО ИК «Энергософт», Екатеринбург, пр. Решетникова, 22а, оф. 206. Выручка 867 млн руб. (2025). 100+ проектов в энергетике</t>
         </is>
       </c>
     </row>
@@ -1061,7 +1101,7 @@
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>Сеть «Креветки и бургеры», Comunale, Морская/10, Pumpula, Jackie. Для СМИ/партнерств: mr@tmr.rest</t>
+          <t>Сеть «Креветки и бургеры», Comunale, Морская/10, Pumpula, Jackie, Рататуй. Для СМИ/партнерств: mr@tmr.rest</t>
         </is>
       </c>
     </row>
@@ -1105,7 +1145,11 @@
         </is>
       </c>
       <c r="K13" s="4" t="inlineStr"/>
-      <c r="L13" s="4" t="inlineStr"/>
+      <c r="L13" s="5" t="inlineStr">
+        <is>
+          <t>КФХ Братцева (разведение овец, зерновые). ООО «Агрохолдинг Братцевых» (зерно). ООО «Бипоинт Логистик» (90% доля, логистика, выручка 660 млн 2024). Адрес: Мамина-Сибиряка, 58, Екатеринбург</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -1122,8 +1166,16 @@
           <t>Сницар Семен</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr"/>
-      <c r="F14" s="2" t="inlineStr"/>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>+7 (343) 268-30-61</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>info@maritol.ru</t>
+        </is>
+      </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
           <t>https://t.me/Semen_Snitsar</t>
@@ -1149,7 +1201,11 @@
           <t>https://maritol.ru/about/</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr"/>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>ООО «Маритоль» (с 2010 г., обслуживание МКД). WhatsApp на сайте. Выручка 251 млн (2024), 17 сотр. Адрес: ул. Победы, 51</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
@@ -1166,8 +1222,16 @@
           <t>Донсков Андрей</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr"/>
-      <c r="F15" s="4" t="inlineStr"/>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>+7 (343) 222-12-32</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>avtoprokat-ekb@mail.ru</t>
+        </is>
+      </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
           <t>https://t.me/ADonskov</t>
@@ -1188,8 +1252,16 @@
           <t>директор и единственный учредитель ООО «Автопрокат Екб»  -  аренда и лизинг легковых автомобилей и лёгких автотранспортных средств</t>
         </is>
       </c>
-      <c r="K15" s="4" t="inlineStr"/>
-      <c r="L15" s="4" t="inlineStr"/>
+      <c r="K15" s="5" t="inlineStr">
+        <is>
+          <t>avtoprokat-ekb.ru</t>
+        </is>
+      </c>
+      <c r="L15" s="5" t="inlineStr">
+        <is>
+          <t>ООО «Автопрокат Екб», аренда легковых авто. Екатеринбург, ул. Сурикова, 7, оф. 1</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -1206,8 +1278,16 @@
           <t>Сафьян Надежда</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr"/>
-      <c r="F16" s="2" t="inlineStr"/>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>+7 (922) 170-07-81</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>2133940@mail.ru</t>
+        </is>
+      </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
           <t>https://t.me/Amallianda</t>
@@ -1234,7 +1314,11 @@
 https://nadezdasafyan.orgs.biz</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr"/>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>К.п.н., гештальт-терапевт. Основатель волонтерского проекта «МыРядом2020» (бесплатная психол. помощь). Приём: Красина 3а, Екатеринбург</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
@@ -1251,7 +1335,11 @@
           <t>Высотский Сергей</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr"/>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>+7 (343) 34x-xx-43</t>
+        </is>
+      </c>
       <c r="F17" s="4" t="inlineStr"/>
       <c r="G17" s="4" t="inlineStr">
         <is>
@@ -1273,8 +1361,16 @@
           <t>учредитель и управляющиц ООО «Мастер Трак» - компания может предоставлять услуги по организации и осуществлению грузовых перевозок, заниматься транспортной обработкой грузов, а также оказывать сопутствующие логистические услуги</t>
         </is>
       </c>
-      <c r="K17" s="4" t="inlineStr"/>
-      <c r="L17" s="4" t="inlineStr"/>
+      <c r="K17" s="5" t="inlineStr">
+        <is>
+          <t>tetratrans.ru</t>
+        </is>
+      </c>
+      <c r="L17" s="5" t="inlineStr">
+        <is>
+          <t>ООО «Мастер Трак» (с 2021 г.). Выручка 112 млн (2024). Грузоперевозки, логистика. Адрес: ул. Кирова, 40б, Екатеринбург</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
@@ -1291,8 +1387,16 @@
           <t>Жуйкова Оксана</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr"/>
-      <c r="F18" s="2" t="inlineStr"/>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>+7 (922) 221-06-76; +7 (343) 521-22-02</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>upr@bani-ekb.ru</t>
+        </is>
+      </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
           <t>https://t.me/Oksana_Zhuikova</t>
@@ -1319,7 +1423,11 @@
           <t>https://kosmosbaniekb.ru/?ysclid=mmktoo9ied38911356</t>
         </is>
       </c>
-      <c r="L18" s="2" t="inlineStr"/>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>ООО «Бани Космос» (55% доля), ООО «Академхолл» (термальный спа-комплекс в Академическом). Адрес бань: ул. Дзержинского, 2</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
@@ -1336,8 +1444,16 @@
           <t>Лунин Станислав</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr"/>
-      <c r="F19" s="4" t="inlineStr"/>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>+7 (343) 287-88-77</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>it@ita1.ru</t>
+        </is>
+      </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
           <t>https://t.me/stas_lunin</t>
@@ -1360,8 +1476,16 @@
 2) ген дир  ООО «КОПИР ПЛЮС» - оптовая торговля компьютерами, периферийными устройствами к компьютерам и программным обеспечением</t>
         </is>
       </c>
-      <c r="K19" s="4" t="inlineStr"/>
-      <c r="L19" s="4" t="inlineStr"/>
+      <c r="K19" s="5" t="inlineStr">
+        <is>
+          <t>ita1.ru</t>
+        </is>
+      </c>
+      <c r="L19" s="5" t="inlineStr">
+        <is>
+          <t>ООО «ИТ Альянс» — мультивендорный системный интегратор. Екатеринбург, пер. Северный, 2А. Работают с Минцифрой, крупными сетями и банками</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
@@ -1383,7 +1507,11 @@
           <t>7 902 409 9449</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr"/>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>info@npcat.ru</t>
+        </is>
+      </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
           <t>https://t.me/Rafail_Valiev</t>
@@ -1404,8 +1532,16 @@
           <t>Ген дир ООО "НПЦ "НОВАТРАНС" - Компания занимается разработкой компьютерного программного обеспечения</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr"/>
-      <c r="L20" s="2" t="inlineStr"/>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>npcat.ru</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>Ген. директор ООО НПЦ «НовАТранс» (с 09.2024). Выручка 196 млн (2024). Разработка VR-тренажёров, электронных курсов. Адрес: ул. Ткачей, 23, оф. 712</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
@@ -1422,8 +1558,16 @@
           <t>Еланцева Елена</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr"/>
-      <c r="F21" s="4" t="inlineStr"/>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>+7 (969) 110-92-86</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>info@moveli.ru</t>
+        </is>
+      </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
           <t>https://t.me/elantseva_helen</t>
@@ -1449,7 +1593,11 @@
           <t>https://www.moveli.ru/page/about-us?ysclid=mmkv8fjfw413881454</t>
         </is>
       </c>
-      <c r="L21" s="4" t="inlineStr"/>
+      <c r="L21" s="5" t="inlineStr">
+        <is>
+          <t>Бренд Moveli — премиальные сумки из натуральной кожи. Магазины в Москве и Екатеринбурге. Адрес: ул. Сакко и Ванцетти, 99</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
@@ -1486,7 +1634,11 @@
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr"/>
-      <c r="L22" s="2" t="inlineStr"/>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>Бывший директор ООО «РП — ГРУПП» и ООО «Монолит Групп» — обе ликвидированы</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
@@ -1503,8 +1655,16 @@
           <t>Пятыгин Сергей</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr"/>
-      <c r="F23" s="4" t="inlineStr"/>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>+7 (343) 382-80-68; +7 (922) 11-00-733</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>info@elittent.org</t>
+        </is>
+      </c>
       <c r="G23" s="4" t="inlineStr"/>
       <c r="H23" s="4" t="inlineStr">
         <is>
@@ -1521,12 +1681,16 @@
           <t>директор и учредитель ООО ГПК «ЭЛИТТЕНТ» - которое занимается изготовлением и обслуживанием промышленных изделий, включая пологи, тенты и другие конструкции</t>
         </is>
       </c>
-      <c r="K23" s="4" t="inlineStr">
-        <is>
-          <t>https://elittent.org/company/</t>
-        </is>
-      </c>
-      <c r="L23" s="4" t="inlineStr"/>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>https://elittent.org/company/; elittent.org</t>
+        </is>
+      </c>
+      <c r="L23" s="5" t="inlineStr">
+        <is>
+          <t>ООО ПК «ЭЛИТТЕНТ» (с 2013 г.). Производство тентов, промизделий. Выручка 27 млн. Адрес: ул. Фронтовых Бригад, 18, к. 3, оф. 222. VK: vk.com/elittent</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
@@ -1544,7 +1708,11 @@
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr"/>
-      <c r="F24" s="2" t="inlineStr"/>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>mr@tmr.rest</t>
+        </is>
+      </c>
       <c r="G24" s="2" t="inlineStr"/>
       <c r="H24" s="2" t="inlineStr">
         <is>
@@ -1562,7 +1730,11 @@
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr"/>
-      <c r="L24" s="2" t="inlineStr"/>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>Управляющий ООО «Новый Вкус (Рататуй)». Адрес: ул. Малышева, 25, Екатеринбург. Филиалы: ул. Восточная, 72; ул. Уральских рабочих, 54</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
@@ -1579,8 +1751,16 @@
           <t>Сизганова Евгения</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr"/>
-      <c r="F25" s="4" t="inlineStr"/>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>+7 (922) 609-16-68</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>info@zemlya-kyrganovo.ru</t>
+        </is>
+      </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
           <t>https://t.me/evgenia_sizganova</t>
@@ -1606,7 +1786,11 @@
           <t>https://kp96.ru/contacts/</t>
         </is>
       </c>
-      <c r="L25" s="4" t="inlineStr"/>
+      <c r="L25" s="5" t="inlineStr">
+        <is>
+          <t>КП «Сакура Парк», с. Курганово, ул. Лавандовая. Закрытая территория, газ, электричество, пруд, рядом р. Чусовая</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
@@ -1623,8 +1807,16 @@
           <t>Телицин Антон</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr"/>
-      <c r="F26" s="2" t="inlineStr"/>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>+7 (953) 04-04-045</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>izi@izi.show</t>
+        </is>
+      </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
           <t>https://t.me/telizin</t>
@@ -1650,7 +1842,11 @@
           <t>https://izi.show/about/</t>
         </is>
       </c>
-      <c r="L26" s="2" t="inlineStr"/>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>IZI.show (с 2008 г.), 3000+ проектов. Звук, свет, сцена для мероприятий. Адрес: ул. Энгельса, 36, оф. 714/1 (Деловой дом Филитцъ)</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
@@ -1690,7 +1886,11 @@
         </is>
       </c>
       <c r="K27" s="4" t="inlineStr"/>
-      <c r="L27" s="4" t="inlineStr"/>
+      <c r="L27" s="5" t="inlineStr">
+        <is>
+          <t>ИП Удельнова И.М. (с 2020 г.), Екатеринбург. ООО «ИМ Диджитал» — электромонтажные работы</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
@@ -1733,12 +1933,16 @@
           <t>Владелец компаний в сфере производства асфальта, разработки мобильных игр, складской недвижимости и инвестиций. Создаю успешные проекты в Екатеринбурге и развиваю партнерские отношения</t>
         </is>
       </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>https://gareev.com</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr"/>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>https://gareev.com; gareev.com, abzred.ru</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>ИП + собственник ООО «АБЗ КРАСНЫЙ» (производство асфальта). 20 направлений бизнеса (аренда, торговля, недвижимость). TenChat: @gareevrr. Возраст 33 года</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="n">
@@ -1755,9 +1959,9 @@
           <t>Дерябина (Рыбкина) Татьяна</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>7 929 220 0197</t>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>7 929 220 0197; +7 (900) 199-97-74</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr"/>
@@ -1782,7 +1986,11 @@
         </is>
       </c>
       <c r="K29" s="4" t="inlineStr"/>
-      <c r="L29" s="4" t="inlineStr"/>
+      <c r="L29" s="5" t="inlineStr">
+        <is>
+          <t>Салон цветов ИП Дерябина Т.Е. Адрес: ул. Академика Бардина, 11Б, 1 этаж, Екатеринбург. Работает круглосуточно, доставка</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
@@ -1818,7 +2026,11 @@
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr"/>
-      <c r="L30" s="2" t="inlineStr"/>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>Информация о текущей деятельности не найдена</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="n">
@@ -1868,7 +2080,7 @@
       <c r="K31" s="4" t="inlineStr"/>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>Развивает гастрономы «Елисейский» (4 точки), «Фабрика еды Гебо», франшиза «Бар здоровых привычек»</t>
+          <t>Бывший владелец сети «Елисей» (закрыта 2022-2023 из-за конкуренции). Сейчас: гастрономы «Елисейский» (4 точки), «Фабрика еды Гебо», франшиза «Бар здоровых привычек». Адрес: ул. Бебеля, 184</t>
         </is>
       </c>
     </row>
@@ -1917,7 +2129,7 @@
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>Холдинг Good Community: Breadway, The Barbara, Tribu, Encore Cafe, гастромолл «Главный». ул. Бориса Ельцина, 6</t>
+          <t>Холдинг Good Community: Breadway, The Barbara, Tribu, Encore Cafe, гастромолл «Главный» (11 тыс. м²). Адрес: ул. Бориса Ельцина, 6. Род. 1980, в ресторанном бизнесе с 1997</t>
         </is>
       </c>
     </row>
@@ -1955,7 +2167,11 @@
         </is>
       </c>
       <c r="K33" s="4" t="inlineStr"/>
-      <c r="L33" s="4" t="inlineStr"/>
+      <c r="L33" s="5" t="inlineStr">
+        <is>
+          <t>ООО «Чистый Город» (с 2015 г.), ген. директор с 10.2023. Мойка автотранспорта. Адрес: ул. Бебеля, 29А, Екатеринбург. Выручка 16 млн (2024)</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
@@ -2025,7 +2241,11 @@
           <t>Вражнов Сергей</t>
         </is>
       </c>
-      <c r="E35" s="4" t="inlineStr"/>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>+7 (922) 198-54-41</t>
+        </is>
+      </c>
       <c r="F35" s="4" t="inlineStr"/>
       <c r="G35" s="4" t="inlineStr">
         <is>
@@ -2052,7 +2272,11 @@
           <t>https://proskladek.ru/?ysclid=mmlxbr7cn9506290060</t>
         </is>
       </c>
-      <c r="L35" s="4" t="inlineStr"/>
+      <c r="L35" s="5" t="inlineStr">
+        <is>
+          <t>ООО «Производственный Склад» (с 2016 г.). Хранение нефтепродуктов, ГСМ. Выручка 216 млн (2024). Офис: ул. Горького, 65, оф. 421. Склад: ул. Фронтовых Бригад, 50А</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
@@ -2069,8 +2293,16 @@
           <t>Габшакурова Регина</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr"/>
-      <c r="F36" s="2" t="inlineStr"/>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>+7 (343) 371-18-30</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>kon@grata-mebel.ru</t>
+        </is>
+      </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
           <t>https://t.me/Lorigina</t>
@@ -2096,7 +2328,11 @@
           <t>https://grata-mebel.ru</t>
         </is>
       </c>
-      <c r="L36" s="2" t="inlineStr"/>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>ООО «Персона Грата» (с 2011 г.). Оптовая торговля офисной мебелью. Адрес: ул. Восточная, 7Г, оф. 414; филиал ул. Луганская, 4</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="n">
@@ -2151,7 +2387,7 @@
       </c>
       <c r="L37" s="5" t="inlineStr">
         <is>
-          <t>Холдинг «ЭМА», Верх-Исетский б-р, 13, Екатеринбург. Экспорт медоборудования в 60+ стран</t>
+          <t>Холдинг «ЭМА», Верх-Исетский б-р, 13, Екатеринбург. Экспорт медоборудования в 60+ стран. Также: добыча ископаемых, строительство, сельхоз, медиа, спорт</t>
         </is>
       </c>
     </row>
@@ -2207,7 +2443,7 @@
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>Креативно-диджитал-агентство 19agency84, ул. Малышева, 71а, оф. 210. ~50-60 чел. в команде</t>
+          <t>Креативно-диджитал-агентство 19agency84 (с 2015 г.), ул. Малышева, 71а, оф. 210. ~50-60 чел. Офисы: Екатеринбург, Москва, Тюмень. TG: @19agency84</t>
         </is>
       </c>
     </row>
@@ -2250,7 +2486,11 @@
         </is>
       </c>
       <c r="K39" s="4" t="inlineStr"/>
-      <c r="L39" s="4" t="inlineStr"/>
+      <c r="L39" s="5" t="inlineStr">
+        <is>
+          <t>Бывший ген. директор ликвидированных компаний «БИГ МЕДИА» и «БИГ МЕДИА КОМПАНИ»</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
@@ -2267,8 +2507,16 @@
           <t>Васин Михаил</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr"/>
-      <c r="F40" s="2" t="inlineStr"/>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>+7 (343) 266-71-66</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>promservis2667166@bk.ru</t>
+        </is>
+      </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
           <t>https://t.me/mikhailvsn</t>
@@ -2294,7 +2542,11 @@
           <t>https://p-service.pro</t>
         </is>
       </c>
-      <c r="L40" s="2" t="inlineStr"/>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>ООО «Пром Сервис» (с 2016 г.). Заготовка/переработка лома чёрных и цветных металлов. 3 лицензии. Офис: ул. Краснолесья, 12А, оф. 501. Склад: г. Берёзовский</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="n">
@@ -2315,7 +2567,11 @@
           <t>Михалицын Андрей</t>
         </is>
       </c>
-      <c r="E41" s="4" t="inlineStr"/>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>+7 (343) 521-51-94; +7 (922) 107-51-94</t>
+        </is>
+      </c>
       <c r="F41" s="4" t="inlineStr"/>
       <c r="G41" s="4" t="inlineStr">
         <is>
@@ -2340,8 +2596,16 @@
 2) Ген дир ООО «МАН ГРУПП» - специализируется на производстве товарного бетона и растворов в Екатеринбурге. Компания также занимается строительством жилых и нежилых зданий и поставляет продукцию на крупные городские объекты</t>
         </is>
       </c>
-      <c r="K41" s="4" t="inlineStr"/>
-      <c r="L41" s="4" t="inlineStr"/>
+      <c r="K41" s="5" t="inlineStr">
+        <is>
+          <t>frame-expert.ru</t>
+        </is>
+      </c>
+      <c r="L41" s="5" t="inlineStr">
+        <is>
+          <t>ООО «ФРЕЙМ» (строительная экспертиза, проектирование), ул. Шейнкмана, 55. ООО «МАН ГРУПП» (товарный бетон, г. Берёзовский). Выручка ФРЕЙМ: экспертиза для строительства</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
@@ -2363,7 +2627,11 @@
           <t>7 922 209 0155</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr"/>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>dorotdel@rambler.ru</t>
+        </is>
+      </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
           <t>https://t.me/OEduard</t>
@@ -2387,7 +2655,11 @@
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr"/>
-      <c r="L42" s="2" t="inlineStr"/>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>Учредитель ООО «ГРИТ» (строительство зданий), ООО «НОВАЯ МАГИСТРАЛЬ» (автодороги, выручка 580 млн 2024, 8 сотр.), ООО «ДЕВАЙС» (перевозки). Адрес: ул. Народной Воли, 62б, оф. 216</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="n">
@@ -2404,8 +2676,16 @@
           <t>Петров Константин</t>
         </is>
       </c>
-      <c r="E43" s="4" t="inlineStr"/>
-      <c r="F43" s="4" t="inlineStr"/>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>8 (800) 600-71-98</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>info@micro-climate.com</t>
+        </is>
+      </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
           <t>https://t.me/ventilator82</t>
@@ -2431,7 +2711,11 @@
           <t>https://micro-climate.com/blog/avtory-bloga/konstantin-petrov</t>
         </is>
       </c>
-      <c r="L43" s="4" t="inlineStr"/>
+      <c r="L43" s="5" t="inlineStr">
+        <is>
+          <t>ООО «Микроклимат» (с 2014 г.), 300+ проектов/год, 50+ сотр. Вентиляция для КРС. Адрес: Елизаветинское ш. 29, оф. 307, Екатеринбург</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
@@ -2473,7 +2757,7 @@
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>ООО «РЕСУРС», Набережные Челны. Оптовая торговля стройматериалами, производство, аренда</t>
+          <t>ООО «РЕСУРС», Набережные Челны. Оптовая торговля стройматериалами, производство бетона/гипса, аренда строительной техники, управление недвижимостью</t>
         </is>
       </c>
     </row>
@@ -2522,7 +2806,7 @@
       </c>
       <c r="L45" s="5" t="inlineStr">
         <is>
-          <t>Эксперт по созданию рентабельных пищевых производств под ключ, Казань</t>
+          <t>ГК «СтандартПродМаш». 15+ лет опыта, 600+ реализованных пищевых производств. Проекты: Агропромпарк «Казань», «Формпласт» и др. Запись на консультацию через сайт</t>
         </is>
       </c>
     </row>
@@ -2545,7 +2829,11 @@
           <t>Шадриков Александр</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr"/>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>+7 (843) 570-40-01</t>
+        </is>
+      </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
           <t>eco@tatar.ru</t>
@@ -2574,7 +2862,7 @@
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>Министр экологии и природных ресурсов РТ с 2018 г. Адрес: ул. Павлюхина, 75, Казань</t>
+          <t>Министр экологии и природных ресурсов РТ с 02.2018. Адрес: ул. Павлюхина, 75, Казань. Род. 01.01.1977, юрист по образованию</t>
         </is>
       </c>
     </row>
@@ -2627,7 +2915,7 @@
       </c>
       <c r="L47" s="5" t="inlineStr">
         <is>
-          <t>Президент Федерации скалолазания РТ. Председатель совета директоров ГК РоманГрупп (1000+ спортплощадок, ~50 парков)</t>
+          <t>Президент Федерации скалолазания РТ. Председатель совета директоров ГК РоманГрупп (1000+ спортплощадок, ~50 парков). ROMAN GROUP — благоустройство, детские площадки</t>
         </is>
       </c>
     </row>
@@ -2669,7 +2957,11 @@
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr"/>
-      <c r="L48" s="2" t="inlineStr"/>
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t>Компания ликвидирована. Казань</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="n">
@@ -2710,7 +3002,11 @@
         </is>
       </c>
       <c r="K49" s="4" t="inlineStr"/>
-      <c r="L49" s="4" t="inlineStr"/>
+      <c r="L49" s="5" t="inlineStr">
+        <is>
+          <t>Учредитель ООО «ТСС ЭНЕРДЖИ» (с 2015 г.), электромонтаж. Текущий директор — Мингазов Э.Э. Адрес: ул. Голубятникова, 20А, Казань. 30 видов деятельности, лицензия на пожарную безопасность</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
@@ -2750,7 +3046,11 @@
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr"/>
-      <c r="L50" s="2" t="inlineStr"/>
+      <c r="L50" s="3" t="inlineStr">
+        <is>
+          <t>Исполнительный директор Федерации шахмат Татарстана. Род. 16.08.1967, Казань. Гроссмейстер (с 1993 г.), рейтинг ФИДЕ 2533</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="n">
@@ -2790,7 +3090,11 @@
         </is>
       </c>
       <c r="K51" s="4" t="inlineStr"/>
-      <c r="L51" s="4" t="inlineStr"/>
+      <c r="L51" s="5" t="inlineStr">
+        <is>
+          <t>ИП Нагуманов А.Ф. (ИНН 165714187604). ИП закрыто 29.02.2012. Был зарегистрирован с 02.06.2006. Направления: электромонтаж, строительство, торговля, общепит, грузоперевозки</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
@@ -2811,8 +3115,16 @@
           <t>Семенихина Арина</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr"/>
-      <c r="F52" s="2" t="inlineStr"/>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>+7 (950) 312-32-03</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>Evadesign@internet.ru</t>
+        </is>
+      </c>
       <c r="G52" s="2" t="inlineStr"/>
       <c r="H52" s="2" t="inlineStr">
         <is>
@@ -2831,7 +3143,11 @@
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr"/>
-      <c r="L52" s="2" t="inlineStr"/>
+      <c r="L52" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЭВО-ХАУС» (аренда недвижимости), ООО «ЭВО-ДИЗАЙН» (архитектура/дизайн). Связано с EVADESIGN. Адрес: ул. Московская, 15, оф. 33, Казань</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="n">
@@ -2871,7 +3187,11 @@
         </is>
       </c>
       <c r="K53" s="4" t="inlineStr"/>
-      <c r="L53" s="4" t="inlineStr"/>
+      <c r="L53" s="5" t="inlineStr">
+        <is>
+          <t>Бухгалтерские услуги, финансовый аудит, налоговое консультирование. Казань</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
@@ -2911,7 +3231,11 @@
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr"/>
-      <c r="L54" s="2" t="inlineStr"/>
+      <c r="L54" s="3" t="inlineStr">
+        <is>
+          <t>ООО «Клиника здоровья и красоты» (г. Казань). Многопрофильная деятельность в сфере медицинских и косметических услуг</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="n">
@@ -2933,7 +3257,11 @@
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr"/>
-      <c r="F55" s="4" t="inlineStr"/>
+      <c r="F55" s="5" t="inlineStr">
+        <is>
+          <t>ildar.mn82@gmail.com</t>
+        </is>
+      </c>
       <c r="G55" s="4" t="inlineStr"/>
       <c r="H55" s="4" t="inlineStr">
         <is>
@@ -2953,7 +3281,11 @@
         </is>
       </c>
       <c r="K55" s="4" t="inlineStr"/>
-      <c r="L55" s="4" t="inlineStr"/>
+      <c r="L55" s="5" t="inlineStr">
+        <is>
+          <t>ООО «ТРИТОН ИНВЕСТ» (аренда недвижимости, с 2021). ООО «ПРОГРЕСС ОЙЛ» (оптовая торговля топливом). ООО «ГЕРМЕС» (грузоперевозки). 12+ компаний, 11+ лет в бизнесе. Адрес: ул. Журналистов, 62, Казань</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
@@ -3009,7 +3341,7 @@
       </c>
       <c r="L56" s="3" t="inlineStr">
         <is>
-          <t>My Corner by Unistroy. Казань, ул. Николая Ершова, 76/1, пом. 109. Часть АО «Джи-групп»</t>
+          <t>My Corner by Unistroy (ООО «Корнер», с 2021). Премиум-загородная недвижимость. Часть АО «Джи-групп». Адрес: ул. Николая Ершова, 76/1, пом. 109, Казань</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3383,11 @@
         </is>
       </c>
       <c r="K57" s="4" t="inlineStr"/>
-      <c r="L57" s="4" t="inlineStr"/>
+      <c r="L57" s="5" t="inlineStr">
+        <is>
+          <t>Компания ликвидирована. Казань</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
@@ -3095,7 +3431,11 @@
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr"/>
-      <c r="L58" s="2" t="inlineStr"/>
+      <c r="L58" s="3" t="inlineStr">
+        <is>
+          <t>ИП ликвидирован. Лесная промышленность, деревообработка. Казань</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="n">
@@ -3139,7 +3479,11 @@
         </is>
       </c>
       <c r="K59" s="4" t="inlineStr"/>
-      <c r="L59" s="4" t="inlineStr"/>
+      <c r="L59" s="5" t="inlineStr">
+        <is>
+          <t>ИП ликвидирован. Строительство, недвижимость. Казань</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
@@ -3193,7 +3537,7 @@
       </c>
       <c r="L60" s="3" t="inlineStr">
         <is>
-          <t>Руководитель Агентства инвестиционного развития РТ с 2014 г. MBA, член Правительства РТ</t>
+          <t>Руководитель Агентства инвестиционного развития РТ с 2014 г. Член Правительства РТ. MBA (Россия, Великобритания). Род. 24.04.1985. Адрес: ул. Агрономическая, 11, Казань</t>
         </is>
       </c>
     </row>
@@ -3249,7 +3593,7 @@
       </c>
       <c r="L61" s="5" t="inlineStr">
         <is>
-          <t>Сооснователь Imagine Group. Казань, ул. Островского, 87, оф. 502. Офисы в Казани и Москве, 55+ сотрудников</t>
+          <t>Сооснователь Imagine Group (ивент-агентство, 55+ сотр.). Казань, ул. Островского, 87, оф. 502. Офисы: Казань, Москва. ИП с 2017</t>
         </is>
       </c>
     </row>
@@ -3305,7 +3649,7 @@
       </c>
       <c r="L62" s="3" t="inlineStr">
         <is>
-          <t>Сооснователь Imagine Group (совместно с Виталием Денисовым). Ивент-агентство, Казань</t>
+          <t>Сооснователь Imagine Group (совместно с Виталием Денисовым). Ивент-агентство, событийный маркетинг. Казань</t>
         </is>
       </c>
     </row>
@@ -3326,7 +3670,7 @@
       </c>
       <c r="E63" s="5" t="inlineStr">
         <is>
-          <t>+7 (831) 412-32-17</t>
+          <t>+7 (831) 412-32-17; +7 (910) 393-47-17</t>
         </is>
       </c>
       <c r="F63" s="5" t="inlineStr">
@@ -3358,7 +3702,7 @@
       </c>
       <c r="L63" s="5" t="inlineStr">
         <is>
-          <t>Ген. директор НПП «Вита-Принт» с 2007 г. Н. Новгород, ул. Бекетова, 13, стр. 3. Выручка 387 млн (2024), 94 сотр.</t>
+          <t>Ген. директор НПП «Вита-Принт» с 2007 г. (25% доля). Полиграфия + электроника. Выручка 387 млн (2024), 94 сотр. Адрес: ул. Бекетова, 13, стр. 3, Н. Новгород</t>
         </is>
       </c>
     </row>
@@ -3410,7 +3754,7 @@
       </c>
       <c r="L64" s="3" t="inlineStr">
         <is>
-          <t>Учредитель ООО «ГЛОБАЛТЕСТ». Саров, ул. Павлика Морозова, 6. Офис в Москве: Долгопрудненское ш., 3</t>
+          <t>Учредитель ООО «ГЛОБАЛТЕСТ» (навигационные, метеорологические приборы). Саров, ул. Павлика Морозова, 6. Офис в Москве: технопарк «Физтехпарк»</t>
         </is>
       </c>
     </row>
@@ -3433,8 +3777,16 @@
           <t>Комиссаров Евгений</t>
         </is>
       </c>
-      <c r="E65" s="4" t="inlineStr"/>
-      <c r="F65" s="4" t="inlineStr"/>
+      <c r="E65" s="5" t="inlineStr">
+        <is>
+          <t>8 (800) 500-58-84</t>
+        </is>
+      </c>
+      <c r="F65" s="5" t="inlineStr">
+        <is>
+          <t>krotov@pts-nn.ru</t>
+        </is>
+      </c>
       <c r="G65" s="4" t="inlineStr"/>
       <c r="H65" s="4" t="inlineStr">
         <is>
@@ -3453,8 +3805,16 @@
 3) ООО «ТАП» - торговля автомобильными деталями, узлами и принадлежностями</t>
         </is>
       </c>
-      <c r="K65" s="4" t="inlineStr"/>
-      <c r="L65" s="4" t="inlineStr"/>
+      <c r="K65" s="5" t="inlineStr">
+        <is>
+          <t>pt-parts.ru</t>
+        </is>
+      </c>
+      <c r="L65" s="5" t="inlineStr">
+        <is>
+          <t>ООО «ПТС НН» (с 2012, выручка 1.96 млрд 2024), ООО «Джон Трак» (с 2021). Запчасти для грузовиков (DAF, MAN, SCANIA, VOLVO). 15+ лет опыта. Адрес: Московское ш. 8, Дзержинск</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
@@ -3509,7 +3869,7 @@
       </c>
       <c r="L66" s="3" t="inlineStr">
         <is>
-          <t>Покидает GASTREET, запустила HORECA HUB. Контакт пресс-службы GASTREET: pr@gastreet.com, тел. 8 (800) 700-93-20</t>
+          <t>Сооснователь и бывший генпродюсер GASTREET International Restaurant Show. Запустила HORECA HUB (клуб, вебинары, гастротуры). PR GASTREET: pr@gastreet.com, тел. 8 (800) 700-93-20</t>
         </is>
       </c>
     </row>
@@ -3570,7 +3930,7 @@
       </c>
       <c r="L67" s="5" t="inlineStr">
         <is>
-          <t>Ген. директор MANTERA с 2023 г. Инвестпортфель 100+ млрд руб., 7.1 млн туристов/год. Сириус, Континентальный пр-кт, 6</t>
+          <t>Ген. директор MANTERA Group с 10.2023. Инвестпортфель 100+ млрд руб., 7.1 млн туристов/год, 6500 сотр. Курорты «Красная Поляна», «Архыз», «Сочи-Парк». Адрес: Сириус, Континентальный пр-кт, 6</t>
         </is>
       </c>
     </row>
@@ -3616,7 +3976,11 @@
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr"/>
-      <c r="L68" s="2" t="inlineStr"/>
+      <c r="L68" s="3" t="inlineStr">
+        <is>
+          <t>PR-директор и соосновательница ресторанной группы Delmar Family (с 2008). Рестораны: Delmar Cafe &amp; Beach, Грильяж (2014), Океан (2019), Мирамар (2021). ИП с 2017</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="n">
@@ -3644,7 +4008,7 @@
       </c>
       <c r="F69" s="5" t="inlineStr">
         <is>
-          <t>pr@kpresort.ru</t>
+          <t>pr@kpresort.ru; sales@kpresort.ru</t>
         </is>
       </c>
       <c r="G69" s="4" t="inlineStr">
@@ -3674,7 +4038,7 @@
       </c>
       <c r="L69" s="5" t="inlineStr">
         <is>
-          <t>Ген. директор Курорта Красная Поляна с 06.2024. Выпускник Сколково. Sales Office Москва: Пресненская наб. 12, стр 2</t>
+          <t>Ген. директор Курорта Красная Поляна с 28.06.2024. Выпускник Сколково. Ранее: игорная зона «Красная Поляна» (2020-2024), 1-й зам. ген. директора MANTERA. Sales Office Москва: Пресненская наб. 12, стр 2, башня Восток, 50 эт.</t>
         </is>
       </c>
     </row>
@@ -3721,7 +4085,11 @@
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr"/>
-      <c r="L70" s="2" t="inlineStr"/>
+      <c r="L70" s="3" t="inlineStr">
+        <is>
+          <t>Директор и учредитель ООО «И-ТУР» (с 2013, туризм/турагент). 17 лет в недвижимости, из них 13 в Сочи. Также ИП (с 2018). TenChat: @irik_sochi</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="n">
@@ -3780,7 +4148,7 @@
       </c>
       <c r="L71" s="5" t="inlineStr">
         <is>
-          <t>Ген. директор Alias Group с 2021. Краснодар, ул. Комсомольская, 15, оф. 126. 118 сотрудников</t>
+          <t>Ген. директор Alias Group (ООО «ЭЛИАС ГРУПП», с 2021). Инвестиционный холдинг: строительство, финансы, пищевая пром., ИТ. 118 сотр. Адрес: ул. Комсомольская, 15, оф. 126, Краснодар</t>
         </is>
       </c>
     </row>
@@ -3822,7 +4190,11 @@
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
-      <c r="L72" s="2" t="inlineStr"/>
+      <c r="L72" s="3" t="inlineStr">
+        <is>
+          <t>ИП (с 2021, аренда недвижимости). Учредитель: ООО «АА ПАРТНЕРС», ООО «СЗ «АА ДЕВЕЛОПМЕНТ ГРУПП» (застройщик), ООО «ПРОМЕТЕЙ АГРО» (с/х, 20% доля, выручка 72.6 млн). Краснодар</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="n">
@@ -3882,7 +4254,7 @@
       </c>
       <c r="L73" s="5" t="inlineStr">
         <is>
-          <t>Директор ООО «ЧФК — Недвижимость» (Черноморская финансовая компания). Краснодар, Красная ул., 108</t>
+          <t>Директор ООО «ЧФК — Недвижимость» (Черноморская финансовая компания, 15+ лет на рынке). Центральный офис: Красная ул., 108, Краснодар. Пн-Пт 9-19, Сб-Вс 10-17</t>
         </is>
       </c>
     </row>
@@ -3934,7 +4306,7 @@
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="3" t="inlineStr">
         <is>
-          <t>ООО «Ванвин». Выручка 205 млн (2024). Витамины, БАД, спортивное питание</t>
+          <t>ООО «Ванвин» (с 2020). Витамины, БАД, спортивное питание. Выручка 205 млн, прибыль 184 млн (2024). Уставный капитал 1 млн. Краснодар</t>
         </is>
       </c>
     </row>
@@ -3987,7 +4359,7 @@
       </c>
       <c r="L75" s="5" t="inlineStr">
         <is>
-          <t>Ген. директор ООО «ИТР» с 02.2025. Краснодар, ул. Октябрьская, 59</t>
+          <t>Ген. директор ООО «ИТР» (Институт транспортного развития, с 02.2025). Инженерные изыскания, проектирование дорожного движения. Адрес: ул. Октябрьская, 59, Краснодар</t>
         </is>
       </c>
     </row>
@@ -4032,10 +4404,14 @@
           <t>директор ООО СК «Екатеринодар-Сити», занимающегося строительством жилых и нежилых зданий.</t>
         </is>
       </c>
-      <c r="K76" s="2" t="inlineStr"/>
+      <c r="K76" s="3" t="inlineStr">
+        <is>
+          <t>uksitigroup.jfservice.ru</t>
+        </is>
+      </c>
       <c r="L76" s="3" t="inlineStr">
         <is>
-          <t>ИП, деятельность агентств недвижимости, строительство. Краснодарский край</t>
+          <t>Директор ООО СК «Екатеринодар-Сити» (с 06.2020). Строительство жилых/нежилых зданий. Уставный капитал 40 млн. Прибыль 203 млн (2025). Адрес: ул. 40-летия Победы, 33г, Краснодар</t>
         </is>
       </c>
     </row>

--- a/Контакты_для_Влада.xlsx
+++ b/Контакты_для_Влада.xlsx
@@ -482,8 +482,8 @@
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="35" customWidth="1" min="9" max="9"/>
     <col width="50" customWidth="1" min="10" max="10"/>
-    <col width="35" customWidth="1" min="11" max="11"/>
-    <col width="50" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="11" max="11"/>
+    <col width="60" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -565,13 +565,21 @@
           <t>Леонтьев Дмитрий</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr"/>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>+7 (343) 283-07-37</t>
+        </is>
+      </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
           <t>https://t.me/Happy_Dmitrii</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr"/>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>asp@altekproekt.ru</t>
+        </is>
+      </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
           <t>Влад</t>
@@ -587,8 +595,16 @@
           <t>директор и учредитель ООО «АЛЬТЕК СТРОЙ ПРОЕКТ» в Екатеринбурге. Компания занимается строительством и оптовой торговлей строительными материалами</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr"/>
-      <c r="L2" s="2" t="inlineStr"/>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>altekproekt.ru</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>Также директор ООО «АЛЬТЕК СИСТЕМС». Офис: ул. Первомайская 15, оф.1201, БЦ Вознесенский, Екатеринбург</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -607,7 +623,11 @@
           <t>Коваленко Светлана</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr"/>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>+7 (343) 345-03-42</t>
+        </is>
+      </c>
       <c r="F3" s="2" t="inlineStr"/>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -636,7 +656,7 @@
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>Экспертиза: торговля, автопром, стройка, недвижимость, экономика малых городов</t>
+          <t>Экспертиза: торговля, автопром, стройка, недвижимость, экономика малых городов. 10 лет исследовательского опыта</t>
         </is>
       </c>
     </row>
@@ -659,7 +679,11 @@
       </c>
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="inlineStr"/>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>info@yarmysheva.ru</t>
+        </is>
+      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Влад</t>
@@ -682,7 +706,7 @@
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>Instagram: @yarmyshevamariya. Журналист по образованию, вела программу «Арт-коктейль fashion» на MTV-Екатеринбург. Замужем за архитектором Дмитрием Реуттом (Проектное бюро R1)</t>
+          <t>Instagram: @yarmyshevamariya. Журналист, вела «Арт-коктейль fashion» на MTV-Екб. Муж — архитектор Дмитрий Реутт (Проектное бюро R1)</t>
         </is>
       </c>
     </row>
@@ -726,7 +750,11 @@
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr"/>
-      <c r="L5" s="2" t="inlineStr"/>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>Бывший ген.дир. Willsun (торговля лесо- и стройматериалами). Компания ликвидирована</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -779,7 +807,7 @@
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>Адвокат, депутат Екатеринбургской городской Думы, руководитель фракции «Единой России». ~1000 волонтеров в центре</t>
+          <t>Адвокат, депутат Екатеринбургской городской Думы, руководитель фракции «Единой России». ~1000 волонтёров в центре. Центры: ул.8 Марта 8д, пр.Сахарова 51</t>
         </is>
       </c>
     </row>
@@ -800,7 +828,11 @@
           <t>Рутковский Евгений</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr"/>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>+7 (343) 226-02-72</t>
+        </is>
+      </c>
       <c r="F7" s="2" t="inlineStr"/>
       <c r="G7" s="2" t="inlineStr"/>
       <c r="H7" s="2" t="inlineStr">
@@ -823,7 +855,11 @@
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr"/>
-      <c r="L7" s="2" t="inlineStr"/>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>ООО «КВАРТА»: ИНН 6678025758, ул.Красный пер. 5/1 оф.7, Екб. Розничная торговля, зарег. 2013</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -843,7 +879,11 @@
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr"/>
-      <c r="F8" s="2" t="inlineStr"/>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>https://t.me/ivanzaichenko</t>
+        </is>
+      </c>
       <c r="G8" s="2" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr">
         <is>
@@ -863,7 +903,7 @@
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>Сеть 100+ магазинов, расширение в Дубай. Активен в медиа (Retail.ru, vc.ru, Реальное время)</t>
+          <t>Telegram-канал «Всякие мысли, Иван Зайченко» (@ivanzaichenko). Instagram: @ivanzaychenko. Также основал «Сушкоф и пицца», IT-систему «Гуляш». 100+ магазинов, расширение в Дубай</t>
         </is>
       </c>
     </row>
@@ -913,7 +953,7 @@
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>Возглавляет Station — теххолдинг с фокусом на Retail Tech, сопредседатель комитета АКАР по новым медиа. Окончил МГУ (ВМК)</t>
+          <t>Возглавляет Station — теххолдинг Retail Tech, сопредседатель комитета АКАР по новым медиа. Окончил МГУ ВМК. Тел. компании: +7 (495) 995-93-13</t>
         </is>
       </c>
     </row>
@@ -953,7 +993,11 @@
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr"/>
-      <c r="L10" s="2" t="inlineStr"/>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>Перешла в Isover из «Бергауф Строительные технологии». Контакты Isover Екб: +7 (343) 310-79-35, info@isover.ru</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -982,7 +1026,11 @@
           <t>https://t.me/vasiliykuz</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr"/>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>info@npcat.ru</t>
+        </is>
+      </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
           <t>Влад</t>
@@ -1003,7 +1051,11 @@
           <t>https://энергософт.рф</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr"/>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>ООО ИК «Энергософт»: 100+ проектов в 55 городах с 2012 г. Выручка 867 млн руб. Адрес: пр-д Решетникова 22а, оф.206</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1048,10 +1100,14 @@
           <t>екатеринбургский ресторатор, основатель и владелец сети ресторанов «Креветки и бургеры», бистор "Морская/10; Итальянское бистро Comunale</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr"/>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>shrmps-brgrs.ru</t>
+        </is>
+      </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>Рестораны: Креветки и Бургеры, Рататуй, Comunale. Для сотрудничества: mr@tmr.rest</t>
+          <t>Рестораны: Креветки и Бургеры (6 точек), Рататуй, Comunale. Для сотрудничества/СМИ: mr@tmr.rest</t>
         </is>
       </c>
     </row>
@@ -1097,7 +1153,11 @@
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr"/>
-      <c r="L13" s="2" t="inlineStr"/>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>Переехал из Екб в Курганскую обл. Ферма ~2000 голов овец романовской породы. Бренд «Ванина Баранина» — полный цикл от выращивания до упаковки</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1116,13 +1176,21 @@
           <t>Сницар Семен</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr"/>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>+7 (343) 268-30-61</t>
+        </is>
+      </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
           <t>https://t.me/Semen_Snitsar</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr"/>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>info@maritol.ru</t>
+        </is>
+      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
           <t>Влад</t>
@@ -1143,7 +1211,11 @@
           <t>https://maritol.ru/about/</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr"/>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>ООО «Маритоль» с 2005/2010 г. WhatsApp: +7 (902) 871-43-43. Офис: ул. Опалихинская 23, Екб. 15+ лет на рынке ЖКХ</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1185,7 +1257,11 @@
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr"/>
-      <c r="L15" s="2" t="inlineStr"/>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>ООО «Автопрокат Екб»: аренда и лизинг легковых авто, Екатеринбург</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1204,13 +1280,21 @@
           <t>Сафьян Надежда</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr"/>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>+7 (922) 170-07-81</t>
+        </is>
+      </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
           <t>https://t.me/Amallianda</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr"/>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>2133940@mail.ru</t>
+        </is>
+      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
           <t>Влад</t>
@@ -1232,7 +1316,11 @@
 https://nadezdasafyan.orgs.biz</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr"/>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>К.п.н., гештальт-терапевт. Основала волонтёрский проект «МыРядом2020» (апрель 2020, Екб) — бесплатная психопомощь. Приём: ул. Красина 3а</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1274,7 +1362,11 @@
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr"/>
-      <c r="L17" s="2" t="inlineStr"/>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>ООО «Мастер Трак»: ИНН 6658542797, ул.Кирова 40б, Екб. Зарег. 24.03.2021</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1321,7 +1413,11 @@
           <t>https://kosmosbaniekb.ru/?ysclid=mmktoo9ied38911356</t>
         </is>
       </c>
-      <c r="L18" s="2" t="inlineStr"/>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>ООО «Академхолл»: строит спа-комплекс 5600 кв.м в Академическом р-не (ул.Рябинина/Краснолесья). 3 этажа: магазины, ресторан 260 мест, хаммам, бассейн, хостел. Также: бани в ККТ «Космос», директор «Андреевских бань»</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1340,13 +1436,21 @@
           <t>Лунин Станислав</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr"/>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>+7 (343) 287-88-77</t>
+        </is>
+      </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
           <t>https://t.me/stas_lunin</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr"/>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>it@ita1.ru</t>
+        </is>
+      </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
           <t>Влад</t>
@@ -1364,8 +1468,16 @@
 2) ген дир  ООО «КОПИР ПЛЮС» - оптовая торговля компьютерами, периферийными устройствами к компьютерам и программным обеспечением</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr"/>
-      <c r="L19" s="2" t="inlineStr"/>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>it-alnc.ru</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>ИТ-Альянс: системный интегратор, 16+ лет. Офис: Северный пер. 2А, Екб. Разработка ПО для финансового сектора</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1394,7 +1506,11 @@
           <t>https://t.me/Rafail_Valiev</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr"/>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>market@npcat.ru</t>
+        </is>
+      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
           <t>Влад</t>
@@ -1410,8 +1526,16 @@
           <t>Ген дир ООО "НПЦ "НОВАТРАНС" - Компания занимается разработкой компьютерного программного обеспечения</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr"/>
-      <c r="L20" s="2" t="inlineStr"/>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>npcat.ru</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>НПЦ «НовАТранс»: 15+ лет, VR-тренажёры, электронные курсы, аппаратные тренажёры для стройки, металлургии, энергетики. Тел: 8 800 333 17 41. Офис: ул.Гоголя 36, оф.804</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1430,13 +1554,21 @@
           <t>Еланцева Елена</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr"/>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>+7 (922) 209-58-98</t>
+        </is>
+      </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
           <t>https://t.me/elantseva_helen</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr"/>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>info@moveli.ru</t>
+        </is>
+      </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
           <t>Влад</t>
@@ -1457,7 +1589,11 @@
           <t>https://www.moveli.ru/page/about-us?ysclid=mmkv8fjfw413881454</t>
         </is>
       </c>
-      <c r="L21" s="2" t="inlineStr"/>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>MOVELI: магазины в Москве (Саларис, Афимолл, Авиапарк), Екб (КД Тихвинъ), СПб (ТЦ Голливуд). Lamoda, Яндекс Маркет, Gold Apple. ИП: ул.Хохрякова 48-51</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1496,7 +1632,11 @@
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr"/>
-      <c r="L22" s="2" t="inlineStr"/>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>ИНН 662316077223. Также: ООО «ИНФО ГРУПП», ООО «ФОЭЛТИ», ООО «МОНОЛИТ ГРУПП». Направления: опт.торговля электротоварами, строительство, обработка данных, управление недвижимостью</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1515,9 +1655,17 @@
           <t>Пятыгин Сергей</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr"/>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>+7 (343) 382-80-68</t>
+        </is>
+      </c>
       <c r="F23" s="2" t="inlineStr"/>
-      <c r="G23" s="2" t="inlineStr"/>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>info@elittent.org</t>
+        </is>
+      </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
           <t>Влад</t>
@@ -1538,7 +1686,11 @@
           <t>https://elittent.org/company/</t>
         </is>
       </c>
-      <c r="L23" s="2" t="inlineStr"/>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>ГПК «ЭЛИТТЕНТ» с 2008 г. Собственная производственная база. Адрес: ул.Фронтовых Бригад 18/3, оф.222. Моб.: +7 (922) 11-00-733</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1559,7 +1711,11 @@
       </c>
       <c r="E24" s="2" t="inlineStr"/>
       <c r="F24" s="2" t="inlineStr"/>
-      <c r="G24" s="2" t="inlineStr"/>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>mr@tmr.rest</t>
+        </is>
+      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
           <t>Влад</t>
@@ -1576,7 +1732,11 @@
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr"/>
-      <c r="L24" s="2" t="inlineStr"/>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>ООО «НОВЫЙ ВКУС» (бренд «Рататуй»): ул.Малышева 25 пом.15. Филиалы: ул.Восточная 72, ул.Уральских рабочих 54. Европейская+русская кухня, доставка</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1595,13 +1755,21 @@
           <t>Сизганова Евгения</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr"/>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>+7 (922) 609-16-68</t>
+        </is>
+      </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
           <t>https://t.me/evgenia_sizganova</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr"/>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>info@zemlya-kyrganovo.ru</t>
+        </is>
+      </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
           <t>Влад</t>
@@ -1622,7 +1790,11 @@
           <t>https://kp96.ru/contacts/</t>
         </is>
       </c>
-      <c r="L25" s="2" t="inlineStr"/>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>КП «Сакура Парк»: с.Курганово, 18 км от Екб, ул.Лавандовая. Офис: ул.Луначарского 80, оф.342. ИП с 2010 г.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1641,13 +1813,21 @@
           <t>Телицин Антон</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr"/>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>8 (953) 04-04-045</t>
+        </is>
+      </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
           <t>https://t.me/telizin</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr"/>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>izi@izi.show</t>
+        </is>
+      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
           <t>Влад</t>
@@ -1668,7 +1848,11 @@
           <t>https://izi.show/about/</t>
         </is>
       </c>
-      <c r="L26" s="2" t="inlineStr"/>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>IZI.show с 2008 г. Офис: ул.Энгельса 36, эт.7, оф.714/1, Деловой дом Филитцъ. Прокат/монтаж звукового, светового и сценического оборудования</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -1710,7 +1894,11 @@
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
-      <c r="L27" s="2" t="inlineStr"/>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>ИП Удельнова И.М.: ИНН 667330758569, зарег. 21.04.2020, Екатеринбург. Электромонтажные работы</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -1760,7 +1948,11 @@
           <t>https://gareev.com</t>
         </is>
       </c>
-      <c r="L28" s="2" t="inlineStr"/>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>Компании: ООО «АБЗ КРАСНЫЙ» (производство асфальта), ООО «ГЕЙМИКС» (разработка ПО/игры, с 2014), ООО «АБЗ АКТИВ». ИП с 2019</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -1806,7 +1998,11 @@
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr"/>
-      <c r="L29" s="2" t="inlineStr"/>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>Салон цветов: ул.Академика Бардина 11Б, 1 эт., Екб. Тел: +7 (900) 199-97-74. Доставка цветов круглосуточно</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -1844,7 +2040,11 @@
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr"/>
-      <c r="L30" s="2" t="inlineStr"/>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>Информация не найдена в открытых источниках</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -1873,7 +2073,11 @@
           <t>https://t.me/aleksandr_ogloblin</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr"/>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>buh4@eliseysm.ru</t>
+        </is>
+      </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
           <t>Влад</t>
@@ -1889,10 +2093,14 @@
           <t>собственник сети супермаркетов «ЕЛИСЕЙ»</t>
         </is>
       </c>
-      <c r="K31" s="2" t="inlineStr"/>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>elisey-mag.ru</t>
+        </is>
+      </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>Сеть «Елисей» основана в 2000 г. По состоянию на 2023 — магазины закрывались из-за конкуренции с федеральными сетями</t>
+          <t>Сеть «Елисей» с 2000 г. По данным 2023 — магазины закрывались из-за конкуренции с федеральными сетями. Адрес: ул.Луначарского 221</t>
         </is>
       </c>
     </row>
@@ -1943,7 +2151,7 @@
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>Good Community: Breadway, The Barbara, Tribu, Encore Cafe. Открывает гастромолл «Главный» (11000 кв.м) в Екатеринбург-Сити</t>
+          <t>Good Community: Breadway, The Barbara, Tribu, Encore Cafe. Открывает гастромолл «Главный» 11000 кв.м в «Екатеринбург-Сити». Юр.адр: ул.Бориса Ельцина 6, пом.28. С 1997 в ресторанном бизнесе</t>
         </is>
       </c>
     </row>
@@ -1983,7 +2191,11 @@
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr"/>
-      <c r="L33" s="2" t="inlineStr"/>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>ООО «Чистый Город»: ИНН 6671027509, ул.Бебеля 29А, Екб. Мойка автотранспорта с 2015 г. Ген.дир с 19.10.2023. Выручка 16.4 млн руб. (2024)</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -2034,7 +2246,11 @@
           <t>https://get.initki.ru</t>
         </is>
       </c>
-      <c r="L34" s="2" t="inlineStr"/>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>ООО «Мотки и Бобины»: онлайн-школа вязания и интернет-магазин пряжи, Екатеринбург</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -2080,7 +2296,11 @@
           <t>https://proskladek.ru/?ysclid=mmlxbr7cn9506290060</t>
         </is>
       </c>
-      <c r="L35" s="2" t="inlineStr"/>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>ООО «Производственный Склад»: ул.Горького 65, оф.421, Екб. Хранение нефтепродуктов, ж/д логистика. Выручка 215.7 млн руб., УК 60.6 млн руб. Лицензия на опасные грузы</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -2099,13 +2319,21 @@
           <t>Габшакурова Регина</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr"/>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>+7 (343) 371-18-30</t>
+        </is>
+      </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
           <t>https://t.me/Lorigina</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr"/>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>kon@grata-mebel.ru</t>
+        </is>
+      </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
           <t>Влад</t>
@@ -2126,7 +2354,11 @@
           <t>https://grata-mebel.ru</t>
         </is>
       </c>
-      <c r="L36" s="2" t="inlineStr"/>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>ГК «Персона Грата»: офисная мебель, оптовая торговля. Офисы: ул.Луганская 4 оф.2; ул.Восточная 7Г оф.414. С 2011</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -2145,13 +2377,21 @@
           <t>Калетин Андрей</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr"/>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>8 (343) 300-40-11</t>
+        </is>
+      </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
           <t>https://t.me/Kaaandrey96</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr"/>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>info@ema.su</t>
+        </is>
+      </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
           <t>Влад</t>
@@ -2173,7 +2413,11 @@
           <t>https://emaholding.ru</t>
         </is>
       </c>
-      <c r="L37" s="2" t="inlineStr"/>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>Холдинг ЭМА: Завод ЭМА (с 1941, медсветильники ЭМАЛЕД, экспорт в 60+ стран), мебельный центр, фитнес-центр. Адрес: Верх-Исетский б-р 13</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -2192,13 +2436,21 @@
           <t>Маркова Екатерина</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr"/>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>+7 (343) 305-19-84</t>
+        </is>
+      </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
           <t>https://t.me/thekatyamarkova</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr"/>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>hello@19agency84.ru</t>
+        </is>
+      </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
           <t>Влад</t>
@@ -2219,7 +2471,11 @@
           <t>https://19agency84.ru</t>
         </is>
       </c>
-      <c r="L38" s="2" t="inlineStr"/>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>19agency84: креативно-диджитальное агентство с 2015. Клиенты: Сбербанк, Магнит, Русагро, Danone. TG: @aloha19agency84. Офис: ул.Малышева 71а, оф.210. Моск.тел: +7 (495) 108-19-84</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -2238,7 +2494,11 @@
           <t>Орлова Екатерина</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr"/>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>+7 (343) 222-07-07</t>
+        </is>
+      </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
           <t>https://t.me/orlova_ka</t>
@@ -2262,7 +2522,11 @@
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr"/>
-      <c r="L39" s="2" t="inlineStr"/>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>Руководила ООО «БИГ МЕДИА» и «БИГ МЕДИА КОМПАНИ» (рекламные агентства, полиграфия). Обе ликвидированы (2025). Адрес: ул.Ткачей 23</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -2308,7 +2572,11 @@
           <t>https://p-service.pro</t>
         </is>
       </c>
-      <c r="L40" s="2" t="inlineStr"/>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>ООО «Пром Сервис»: ИНН 6685122022, ул.Белинского 222/94. Опт.торговля ломом, переработка металлов. 3 лицензии. Выручка 222.6 млн руб., прибыль 7.3 млн руб. (2025)</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -2331,7 +2599,11 @@
           <t>Михалицын Андрей</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr"/>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>+7 (343) 521-51-94</t>
+        </is>
+      </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
           <t>https://t.me/mixalitsin</t>
@@ -2357,7 +2629,11 @@
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr"/>
-      <c r="L41" s="2" t="inlineStr"/>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ФРЕЙМ»: ИНН 6678048723, с 2014. Строительная экспертиза, согласование перепланировок. Офис: ул.Шейнкмана 55. Моб: +7 (922) 107-51-94</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -2405,7 +2681,11 @@
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr"/>
-      <c r="L42" s="2" t="inlineStr"/>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ГРИТ»: ИНН 6671242432, ул.Шаумяна 83, пом.203, Екб. Строительство, лесозаготовки, добыча полезных ископаемых. УК 100 тыс.руб., доля 90%. Также ИП (аренда недвижимости)</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -2424,13 +2704,21 @@
           <t>Петров Константин</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr"/>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>+7 (343) 237-27-72</t>
+        </is>
+      </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
           <t>https://t.me/ventilator82</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr"/>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>kp09@mail.ru</t>
+        </is>
+      </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
           <t>Влад</t>
@@ -2451,7 +2739,11 @@
           <t>https://micro-climate.com/blog/avtory-bloga/konstantin-petrov</t>
         </is>
       </c>
-      <c r="L43" s="2" t="inlineStr"/>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t>ООО «Микроклимат» с 2014: системы вентиляции для животноводческих комплексов. Также: micro-clim.ru. Адрес: ул.Белореченская 12А</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -2493,7 +2785,11 @@
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr"/>
-      <c r="L44" s="2" t="inlineStr"/>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>ООО «РЕСУРС»: опт.торговля стройматериалами, производство ж/б изделий, аренда стройтехники, управление недвижимостью. Набережные Челны</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -2550,7 +2846,7 @@
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t>Управляющий собственник ГК «СтандартПродМаш». Выпускница Сколково, член генсовета Деловой России. 600+ пищевых производств за 15 лет</t>
+          <t>Управляющий собственник ГК «СтандартПродМаш». Выпускница Сколково, член генсовета Деловой России. 600+ пищевых производств за 15 лет. Тел. компании: 8 (800) 7000-388</t>
         </is>
       </c>
     </row>
@@ -2575,9 +2871,17 @@
           <t>Шадриков Александр</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr"/>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>+7 (843) 267-68-01</t>
+        </is>
+      </c>
       <c r="F46" s="2" t="inlineStr"/>
-      <c r="G46" s="2" t="inlineStr"/>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>eco@tatar.ru</t>
+        </is>
+      </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
           <t>Влад</t>
@@ -2593,10 +2897,14 @@
           <t>Министр экологии и природных ресурсов Республики Татарстан.</t>
         </is>
       </c>
-      <c r="K46" s="2" t="inlineStr"/>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>eco.tatarstan.ru</t>
+        </is>
+      </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>Министр с 08.02.2018. Род. 01.01.1977, с. Старое Дрожжаное. Контакт ведомства: eco.tatarstan.ru, ул. Павлюхина 75, Казань</t>
+          <t>Министр экологии РТ с 08.02.2018. Род. 01.01.1977, с.Старое Дрожжаное. Офис: ул.Павлюхина 75, Казань 420049</t>
         </is>
       </c>
     </row>
@@ -2655,7 +2963,7 @@
       </c>
       <c r="L47" s="3" t="inlineStr">
         <is>
-          <t>Федерация: ул. Дубравная 2Б оф.4, Казань</t>
+          <t>Также зам.министра цифрового развития РТ. Федерация скалолазания: ул.Дубравная 2Б оф.4, Казань</t>
         </is>
       </c>
     </row>
@@ -2699,7 +3007,11 @@
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr"/>
-      <c r="L48" s="2" t="inlineStr"/>
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t>ИП: ИНН 165031102860, с 2017. Деятельность головных офисов, консалтинг, холдинги. Директор ООО ПКФ «РОСТ»</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -2749,10 +3061,14 @@
 Компания выполняет полный цикл электромонтажных и энергетических работ — от проектирования до сдачи объекта в эксплуатацию.</t>
         </is>
       </c>
-      <c r="K49" s="2" t="inlineStr"/>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t>tssenergy.ru</t>
+        </is>
+      </c>
       <c r="L49" s="3" t="inlineStr">
         <is>
-          <t>ТСС Энерджи: выручка 206 млн руб. (2024). Адрес: ул. Гвардейская 45, Казань</t>
+          <t>ТСС Энерджи: выручка 206 млн руб. (2024). Полный цикл электромонтажных работ. Адрес: ул.Гвардейская 45, Казань</t>
         </is>
       </c>
     </row>
@@ -2796,7 +3112,11 @@
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr"/>
-      <c r="L50" s="2" t="inlineStr"/>
+      <c r="L50" s="3" t="inlineStr">
+        <is>
+          <t>Ильдар Рифкатович Ибрагимов — шахматный гроссмейстер из Казани (род. 1967). Исп. директор федерации шахмат РТ</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -2838,7 +3158,11 @@
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr"/>
-      <c r="L51" s="2" t="inlineStr"/>
+      <c r="L51" s="3" t="inlineStr">
+        <is>
+          <t>ИП: ИНН 165714187604, зарег. 02.06.2006 — закрыт 29.02.2012. Направления: электромонтаж, строительство, торговля, ресторанный бизнес</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -2881,7 +3205,11 @@
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr"/>
-      <c r="L52" s="2" t="inlineStr"/>
+      <c r="L52" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ЭВО-ХАУС»: аренда и управление недвижимостью, Казань</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -2923,7 +3251,11 @@
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr"/>
-      <c r="L53" s="2" t="inlineStr"/>
+      <c r="L53" s="3" t="inlineStr">
+        <is>
+          <t>Бухгалтерский учёт, финансовый аудит, налоговое консультирование, Казань</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -2971,7 +3303,7 @@
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="3" t="inlineStr">
         <is>
-          <t>Также зарегистрирован ИП: туристические услуги, парикмахерские услуги</t>
+          <t>ООО «Клиника здоровья и красоты», Казань. Также ИП: туристические услуги, парикмахерские услуги</t>
         </is>
       </c>
     </row>
@@ -3023,7 +3355,7 @@
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="3" t="inlineStr">
         <is>
-          <t>Также директор ООО «Тритон Трейд», ООО «Промстрой» и др. Адрес: ул. Журналистов 62, Казань</t>
+          <t>ООО «ТРИТОН ИНВЕСТ»: ул.Журналистов 62, Казань. Аренда/управление нежилым имуществом. Также: «Тритон Трейд», «Промстрой»</t>
         </is>
       </c>
     </row>
@@ -3083,7 +3415,7 @@
       </c>
       <c r="L56" s="3" t="inlineStr">
         <is>
-          <t>10+ лет в строительной отрасли. Образование: КГФЭИ, КФУ, Сколково</t>
+          <t>My Corner by Unistroy: коттеджные посёлки премиум-класса, Казань. 10+ лет в строительной отрасли. Образование: КГФЭИ, КФУ, Сколково. VK: vk.com/mycorner_by_unistroy</t>
         </is>
       </c>
     </row>
@@ -3127,7 +3459,11 @@
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr"/>
-      <c r="L57" s="2" t="inlineStr"/>
+      <c r="L57" s="3" t="inlineStr">
+        <is>
+          <t>Директор ООО «АК БАРС ИНЖИНИРИНГ» (строительство, ИНН 1657125304, выручка 413 млн руб.) и ООО «СИТИ ПРОЕКТ» (инженерные коммуникации). 146-е место в рейтинге ген.директоров стройотрасли РТ</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -3173,7 +3509,11 @@
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr"/>
-      <c r="L58" s="2" t="inlineStr"/>
+      <c r="L58" s="3" t="inlineStr">
+        <is>
+          <t>ИП с 2016, Сабинский р-н РТ. Консалтинг, строительство, торговля лесо-/стройматериалами, займы, недвижимость. Совокупная выручка 28.3 млн руб. (2024)</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -3219,7 +3559,11 @@
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr"/>
-      <c r="L59" s="2" t="inlineStr"/>
+      <c r="L59" s="3" t="inlineStr">
+        <is>
+          <t>Сопредседатель Деловой России по РТ. Специализация: упаковка бизнесов во франшизы (400+ проектов с 2013). Образование: КНИТУ-КАИ, Lincoln University (eMBA). Опыт маркетинга: Mercedes, МТС, МегаФон</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -3268,10 +3612,14 @@
           <t>Руководитель Агентства инвестиционного развития Республики Татарстан</t>
         </is>
       </c>
-      <c r="K60" s="2" t="inlineStr"/>
+      <c r="K60" s="3" t="inlineStr">
+        <is>
+          <t>tida.tatarstan.ru</t>
+        </is>
+      </c>
       <c r="L60" s="3" t="inlineStr">
         <is>
-          <t>Член Правительства РТ. MBA в Великобритании, выпускница Сколково, Стэнфорда. В должности с 2014 г.</t>
+          <t>Член Правительства РТ. MBA Великобритания, выпускница Сколково, Стэнфорда. В должности с 2014. Офис: ул.Агрономическая 11, Казань</t>
         </is>
       </c>
     </row>
@@ -3329,7 +3677,7 @@
       </c>
       <c r="L61" s="3" t="inlineStr">
         <is>
-          <t>Imagine Group: 50+ человек, 1500+ проектов с 2013 г. TG: @IMG_Event</t>
+          <t>Imagine Group: 50+ человек, 1500+ проектов с 2013. TG: @IMG_Event. Офис: ул.Большая Красная 13, Казань</t>
         </is>
       </c>
     </row>
@@ -3387,7 +3735,7 @@
       </c>
       <c r="L62" s="3" t="inlineStr">
         <is>
-          <t>Сооснователь Imagine Group совместно с Денисовым Виталием</t>
+          <t>Сооснователь Imagine Group совместно с Денисовым Виталием. Ивенты, внешние коммуникации, HR-бренд</t>
         </is>
       </c>
     </row>
@@ -3431,10 +3779,14 @@
 Компания занимается полиграфической деятельностью, а также имеет дополнительные направления, включая производство интегральных электронных схем и научные исследования</t>
         </is>
       </c>
-      <c r="K63" s="2" t="inlineStr"/>
+      <c r="K63" s="3" t="inlineStr">
+        <is>
+          <t>vita-print.com</t>
+        </is>
+      </c>
       <c r="L63" s="3" t="inlineStr">
         <is>
-          <t>НПП Вита-Принт: ул. Бекетова 13/3, Нижний Новгород. Работают с 1994 г.</t>
+          <t>НПП «Вита-Принт» с 1994 г.: ул.Бекетова 13/3, Н.Новгород. Полиграфия, производство интегральных электронных схем. Моб.: +7 (910) 393-47-17. TG, Viber, WhatsApp</t>
         </is>
       </c>
     </row>
@@ -3481,10 +3833,14 @@
           <t>Учредитель ООО «ГЛОБАЛТЕСТ». Компания зарегистрирована в Сарове Нижегородской области, занимается производством навигационных, метеорологических, геодезических, геофизических и аналогичных приборов, аппаратуры и инструментов</t>
         </is>
       </c>
-      <c r="K64" s="2" t="inlineStr"/>
+      <c r="K64" s="3" t="inlineStr">
+        <is>
+          <t>globaltest.ru</t>
+        </is>
+      </c>
       <c r="L64" s="3" t="inlineStr">
         <is>
-          <t>Глобалтест: ул. Павлика Морозова 6, Саров. Тел: +7 (83130) 6-77-77. Моск. офис: 2-й Павелецкий пр-д 5с1</t>
+          <t>ООО «ГЛОБАЛТЕСТ»: ул.Павлика Морозова 6, Саров. Навигационные, метеорологические, геодезические приборы. Моск.офис: 2-й Павелецкий пр-д 5с1 оф.413, +7 (916) 958-20-37</t>
         </is>
       </c>
     </row>
@@ -3532,7 +3888,7 @@
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="3" t="inlineStr">
         <is>
-          <t>ПТС НН: уставной капитал 7.5 млн руб., 80 сотрудников, доход 1.39 млрд руб. (2021). Совладелец 50/50 с Вадимом Комиссаровым</t>
+          <t>ООО «ПТС НН» (Приволжье-ТрансСервис НН): ИНН 5263092995, Дзержинск. УК 7.5 млн руб., 80 сотрудников, доход 1.39 млрд руб. (2021). Совладелец 50/50 с Вадимом Комиссаровым. Также: «Джон Трак», «ТАП»</t>
         </is>
       </c>
     </row>
@@ -3587,7 +3943,7 @@
       </c>
       <c r="L66" s="3" t="inlineStr">
         <is>
-          <t>Также основатель бизнес-школы #ДРУГАЯ. Аккаунт Clubhouse: @sufiyanovae. GASTREET 7-12 июня 2026 Сочи, 5500+ участников</t>
+          <t>Также основатель бизнес-школы #ДРУГАЯ. Clubhouse: @sufiyanovae. GASTREET 7-12 июня 2026 Сочи, 5500+ участников. Тел. GASTREET: 8 (800) 700-93-20</t>
         </is>
       </c>
     </row>
@@ -3642,7 +3998,7 @@
       </c>
       <c r="L67" s="3" t="inlineStr">
         <is>
-          <t>В Mantera с окт.2023. Ранее: предcедатель совета директоров АО «Сочи-Парк», ген.дир. ООО «Курорт плюс» (Горки Город). Инвестпортфель 100+ млрд руб.</t>
+          <t>В Mantera с окт.2023. Ранее: председатель совета директоров АО «Сочи-Парк», ген.дир ООО «Курорт плюс» (Горки Город). Инвестпортфель 100+ млрд руб. Тел: 8 (800) 100-78-62</t>
         </is>
       </c>
     </row>
@@ -3688,7 +4044,7 @@
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="3" t="inlineStr">
         <is>
-          <t>PR-директор сети ресторанов Delmar Family в Сочи (кафе «Дель Мар», ресторан «Грильяж» и др.). Запуск ресторана «ОКЕАН»</t>
+          <t>PR-директор сети ресторанов Delmar Family в Сочи (кафе «Дель Мар», ресторан «Грильяж»). Запуск ресторана «ОКЕАН» на ул.Воровского</t>
         </is>
       </c>
     </row>
@@ -3715,7 +4071,11 @@
           <t>нет</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr"/>
+      <c r="G69" s="3" t="inlineStr">
+        <is>
+          <t>pr@kpresort.ru</t>
+        </is>
+      </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
           <t>Влад</t>
@@ -3731,10 +4091,14 @@
           <t>новый генеральный директор курорта «Красная Поляна» в Сочи</t>
         </is>
       </c>
-      <c r="K69" s="2" t="inlineStr"/>
+      <c r="K69" s="3" t="inlineStr">
+        <is>
+          <t>krasnayapolyanaresort.ru</t>
+        </is>
+      </c>
       <c r="L69" s="3" t="inlineStr">
         <is>
-          <t>Возглавил курорт 28.06.2024. Из Владимира, 42 года. С 2020 возглавлял игорную зону «Красная Поляна». Пресс-служба: pr@kpresort.ru</t>
+          <t>Возглавил курорт 28.06.2024. Из Владимира, род. ~1982. С 2020 возглавлял игорную зону «Красная Поляна». 1-й зам ген.дир Mantera. Тел курорта: +7 (800) 550-20-20</t>
         </is>
       </c>
     </row>
@@ -3779,7 +4143,11 @@
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr"/>
-      <c r="L70" s="2" t="inlineStr"/>
+      <c r="L70" s="3" t="inlineStr">
+        <is>
+          <t>ООО «И-ТУР»: ИНН 2320210226, с 2013, Сочи. Туризм, обслуживание помещений, недвижимость, доп.образование. Предпринимательский стаж 18+ лет. TenChat: @irik_sochi</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -3833,10 +4201,14 @@
 Alias Group — инвестиционный холдинг, который объединяет активы из различных секторов экономики</t>
         </is>
       </c>
-      <c r="K71" s="2" t="inlineStr"/>
+      <c r="K71" s="3" t="inlineStr">
+        <is>
+          <t>bsfc.com</t>
+        </is>
+      </c>
       <c r="L71" s="3" t="inlineStr">
         <is>
-          <t>Alias Group: 7 городов, 11 направлений, 1500+ сотрудников, портфель ~70 млрд руб. Ключевой актив — девелопер «Неометрия»</t>
+          <t>Alias Group: 7 городов, 11 направлений, 1500+ сотрудников, портфель ~70 млрд руб. Ключевой актив — девелопер «Неометрия». Офис: ул.Красная 108, Краснодар</t>
         </is>
       </c>
     </row>
@@ -3861,7 +4233,11 @@
           <t>Горелова Анна</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr"/>
+      <c r="E72" s="3" t="inlineStr">
+        <is>
+          <t>+7 (800) 300-48-84</t>
+        </is>
+      </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
           <t>нет</t>
@@ -3879,8 +4255,16 @@
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
-      <c r="K72" s="2" t="inlineStr"/>
-      <c r="L72" s="2" t="inlineStr"/>
+      <c r="K72" s="3" t="inlineStr">
+        <is>
+          <t>aa-partners.ru</t>
+        </is>
+      </c>
+      <c r="L72" s="3" t="inlineStr">
+        <is>
+          <t>AA Partners: архитектурно-проектное бюро, Краснодар. Также: ООО «СЗ АА ДЕВЕЛОПМЕНТ ГРУПП», ООО «ПРОМЕТЕЙ АГРО». Доп.тел: +7 (939) 464-32-35</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -3935,10 +4319,14 @@
 Некоторые дополнительные виды деятельности: покупка и продажа собственного недвижимого имущества, подготовка к продаже собственного нежилого недвижимого имущества, покупка и продажа собственных нежилых зданий и помещений, покупка и продажа земельных участков</t>
         </is>
       </c>
-      <c r="K73" s="2" t="inlineStr"/>
+      <c r="K73" s="3" t="inlineStr">
+        <is>
+          <t>bsfc.com</t>
+        </is>
+      </c>
       <c r="L73" s="3" t="inlineStr">
         <is>
-          <t>ЧФК — Черноморская финансовая компания. Офис: ул. Красная 108, Краснодар</t>
+          <t>ООО «ЧФК — Недвижимость» (Черноморская финансовая компания): инвестиции, недвижимость, 23 года в бизнесе. Офис: ул.Красная 108, Краснодар</t>
         </is>
       </c>
     </row>
@@ -3992,7 +4380,7 @@
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="3" t="inlineStr">
         <is>
-          <t>ООО Ванвин: выручка 205 млн руб. (2024), прибыль 183 млн руб. Уставный капитал 1 млн руб.</t>
+          <t>ООО «Ванвин»: витамины и продукты для здоровья. Выручка 205 млн руб., прибыль 183 млн руб. (2024). УК 1 млн руб. Адрес: ул.Жлобы 141, Краснодар</t>
         </is>
       </c>
     </row>
@@ -4045,7 +4433,11 @@
           <t>https://itr2050.ru/komanda.html</t>
         </is>
       </c>
-      <c r="L75" s="2" t="inlineStr"/>
+      <c r="L75" s="3" t="inlineStr">
+        <is>
+          <t>ООО «ИТР» (Институт транспортного развития): инженерные изыскания, проектирование, строительный контроль. Адрес: ул.Октябрьская 59, Краснодар. Также директор по развитию ООО «Центр дорожных инноваций» (ИТС, светофоры)</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -4091,7 +4483,11 @@
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr"/>
-      <c r="L76" s="2" t="inlineStr"/>
+      <c r="L76" s="3" t="inlineStr">
+        <is>
+          <t>ООО СК «Екатеринодар-Сити»: строительство жилых/нежилых зданий. ИП: ИНН 231103860276, с 2016. Агентство недвижимости, строительство, проектирование</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:L76"/>
